--- a/sheets/대금율보/검수/쇼스타코비치 왈츠 2번.xlsx
+++ b/sheets/대금율보/검수/쇼스타코비치 왈츠 2번.xlsx
@@ -8704,7 +8704,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -8784,7 +8784,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 洟
 淋</t>
         </is>
@@ -8792,7 +8792,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 洟
 淋</t>
         </is>
@@ -8947,7 +8947,7 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -9014,7 +9014,7 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 潕</t>
         </is>
       </c>
@@ -9022,7 +9022,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 潕</t>
         </is>
       </c>
@@ -9082,7 +9082,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林
 南</t>
         </is>
@@ -9130,7 +9130,7 @@
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 太
 㽔</t>
         </is>
@@ -9174,7 +9174,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9182,7 +9182,7 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="S10" s="23"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林
 南</t>
         </is>
@@ -9326,7 +9326,7 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9334,7 +9334,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9480,7 +9480,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -9488,7 +9488,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -9756,7 +9756,7 @@
       <c r="O16" s="23"/>
       <c r="P16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林
 南</t>
         </is>
@@ -9800,7 +9800,7 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9808,7 +9808,7 @@
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 無</t>
         </is>
       </c>
@@ -9926,7 +9926,7 @@
       <c r="S18" s="29"/>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 太
 㽔</t>
         </is>
@@ -10030,7 +10030,7 @@
       <c r="O22" s="23"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 太
 㽔</t>
         </is>
@@ -10394,7 +10394,7 @@
       <c r="Q30" s="22"/>
       <c r="R30" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林
 南</t>
         </is>

--- a/sheets/대금율보/검수/쇼스타코비치 왈츠 2번.xlsx
+++ b/sheets/대금율보/검수/쇼스타코비치 왈츠 2번.xlsx
@@ -8639,32 +8639,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="U15" s="28"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="U17" s="24"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
       </c>
       <c r="U18" s="29"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="81.63" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="91.25" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="91.25" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="91.25" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="24"/>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="U23" s="26"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="91.25" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="91.25" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="U25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="91.25" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="24"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="U26" s="24"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="91.25" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="91.25" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="23"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="U28" s="23"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="91.25" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="24"/>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="U29" s="24"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="91.25" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="U30" s="22"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="91.25" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="91.25" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="91.25" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="91.25" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="91.25" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="24"/>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="U35" s="24"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="91.25" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="29"/>
@@ -10654,7 +10654,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
